--- a/hackers scoreboard.xlsx
+++ b/hackers scoreboard.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{2F60A2A1-D7F9-754C-99D1-665FF5CB571C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{908F7CB2-722E-964E-9AAB-7E04859A2237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Hacker</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>Eymen Ensar Efe</t>
+  </si>
+  <si>
+    <t>Bonus</t>
   </si>
 </sst>
 </file>
@@ -134,7 +137,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,12 +147,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -168,6 +165,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -266,22 +275,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -618,10 +627,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD8F6719-0A62-1343-B876-55FAB151758A}">
-  <dimension ref="A2:O14"/>
+  <dimension ref="A2:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.10546875" customWidth="1"/>
+    <col min="2" max="2" width="13.046875" customWidth="1"/>
     <col min="3" max="3" width="4.4375" style="3" customWidth="1"/>
     <col min="4" max="4" width="7.12890625" style="3" customWidth="1"/>
     <col min="5" max="5" width="4.83984375" style="3" customWidth="1"/>
@@ -630,11 +639,15 @@
     <col min="8" max="8" width="4.70703125" style="3" customWidth="1"/>
     <col min="9" max="9" width="4.4375" style="3" customWidth="1"/>
     <col min="10" max="10" width="6.45703125" style="3" customWidth="1"/>
-    <col min="11" max="13" width="8.609375" style="3"/>
-    <col min="14" max="14" width="9.4140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="8.609375" style="3"/>
+    <col min="12" max="12" width="6.1875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.45703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.4140625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="5.51171875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -672,16 +685,19 @@
         <v>11</v>
       </c>
       <c r="M2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="O2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -689,48 +705,51 @@
         <v>15</v>
       </c>
       <c r="C3" s="2">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2">
         <v>4</v>
       </c>
-      <c r="D3" s="2">
+      <c r="H3" s="2">
+        <v>8</v>
+      </c>
+      <c r="I3" s="2">
+        <v>3</v>
+      </c>
+      <c r="J3" s="2">
+        <v>7</v>
+      </c>
+      <c r="K3" s="2">
         <v>6</v>
       </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2">
-        <v>3</v>
-      </c>
-      <c r="I3" s="2">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2">
-        <v>5</v>
-      </c>
-      <c r="K3" s="2">
-        <v>3</v>
-      </c>
       <c r="L3" s="2">
-        <v>1</v>
-      </c>
-      <c r="M3" s="12">
-        <f>SUM(C3:L3)</f>
-        <v>29</v>
+        <v>2</v>
+      </c>
+      <c r="M3" s="2">
+        <v>2</v>
       </c>
       <c r="N3" s="11">
-        <v>15</v>
+        <f>SUM(C3:M3)</f>
+        <v>52</v>
       </c>
       <c r="O3" s="10">
-        <f>M3*100+N3*25</f>
-        <v>3275</v>
+        <v>18</v>
+      </c>
+      <c r="P3" s="9">
+        <f>N3*100+O3*25</f>
+        <v>5650</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -738,46 +757,49 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" s="2">
         <v>3</v>
       </c>
       <c r="J4" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K4" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L4" s="2">
-        <v>1</v>
-      </c>
-      <c r="M4" s="12">
-        <f>SUM(C4:L4)</f>
-        <v>24</v>
+        <v>2</v>
+      </c>
+      <c r="M4" s="2">
+        <v>1</v>
       </c>
       <c r="N4" s="11">
-        <v>3</v>
+        <f>SUM(C4:M4)</f>
+        <v>41</v>
       </c>
       <c r="O4" s="10">
-        <f>M4*100+N4*25</f>
-        <v>2475</v>
+        <v>5</v>
+      </c>
+      <c r="P4" s="9">
+        <f>N4*100+O4*25</f>
+        <v>4225</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -785,67 +807,72 @@
         <v>17</v>
       </c>
       <c r="C5" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" s="2">
+        <v>6</v>
+      </c>
+      <c r="K5" s="2">
+        <v>3</v>
+      </c>
+      <c r="L5" s="2">
+        <v>2</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="11">
+        <f>SUM(C5:M5)</f>
+        <v>34</v>
+      </c>
+      <c r="O5" s="10">
+        <v>8</v>
+      </c>
+      <c r="P5" s="9">
+        <f>N5*100+O5*25</f>
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" s="12">
         <v>4</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2">
-        <v>1</v>
-      </c>
-      <c r="M5" s="12">
-        <f>SUM(C5:L5)</f>
-        <v>16</v>
-      </c>
-      <c r="N5" s="11">
-        <v>3</v>
-      </c>
-      <c r="O5" s="10">
-        <f>M5*100+N5*25</f>
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="13">
-        <v>4</v>
-      </c>
       <c r="B6" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
       </c>
-      <c r="F6" s="2"/>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
       <c r="G6" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
@@ -854,281 +881,320 @@
         <v>5</v>
       </c>
       <c r="K6" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L6" s="2">
         <v>1</v>
       </c>
-      <c r="M6" s="12">
-        <f>SUM(C6:L6)</f>
-        <v>15</v>
+      <c r="M6" s="2">
+        <v>1</v>
       </c>
       <c r="N6" s="11">
+        <f>SUM(C6:M6)</f>
+        <v>32</v>
+      </c>
+      <c r="O6" s="10">
+        <v>7</v>
+      </c>
+      <c r="P6" s="9">
+        <f>N6*100+O6*25</f>
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" s="12">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2">
+        <v>7</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2">
+        <v>3</v>
+      </c>
+      <c r="K7" s="2">
         <v>4</v>
       </c>
-      <c r="O6" s="10">
-        <f>M6*100+N6*25</f>
-        <v>1600</v>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2">
+        <v>1</v>
+      </c>
+      <c r="N7" s="11">
+        <f>SUM(C7:M7)</f>
+        <v>24</v>
+      </c>
+      <c r="O7" s="10">
+        <v>3</v>
+      </c>
+      <c r="P7" s="9">
+        <f>N7*100+O7*25</f>
+        <v>2475</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="13">
-        <v>5</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2">
-        <v>3</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2">
-        <v>1</v>
-      </c>
-      <c r="M7" s="12">
-        <f>SUM(C7:L7)</f>
-        <v>13</v>
-      </c>
-      <c r="N7" s="11">
-        <v>1</v>
-      </c>
-      <c r="O7" s="10">
-        <f>M7*100+N7*25</f>
-        <v>1325</v>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8" s="12">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>3</v>
+      </c>
+      <c r="H8" s="2">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2">
+        <v>2</v>
+      </c>
+      <c r="J8" s="2">
+        <v>4</v>
+      </c>
+      <c r="K8" s="2">
+        <v>2</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="11">
+        <f>SUM(C8:M8)</f>
+        <v>23</v>
+      </c>
+      <c r="O8" s="10">
+        <v>2</v>
+      </c>
+      <c r="P8" s="9">
+        <f>N8*100+O8*25</f>
+        <v>2350</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="13">
-        <v>6</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2">
-        <v>3</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2">
-        <v>3</v>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2">
-        <v>3</v>
-      </c>
-      <c r="K8" s="2">
-        <v>2</v>
-      </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="12">
-        <f>SUM(C8:L8)</f>
-        <v>13</v>
-      </c>
-      <c r="N8" s="11">
-        <v>1</v>
-      </c>
-      <c r="O8" s="10">
-        <f>M8*100+N8*25</f>
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="8">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A9" s="13">
         <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
       <c r="D9" s="2">
-        <v>4</v>
-      </c>
-      <c r="E9" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K9" s="2">
-        <v>1</v>
-      </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="12">
-        <f>SUM(C9:L9)</f>
-        <v>11</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2"/>
       <c r="N9" s="11">
-        <v>2</v>
-      </c>
-      <c r="O9" s="10">
-        <f>M9*100+N9*25</f>
-        <v>1150</v>
+        <f>SUM(C9:M9)</f>
+        <v>23</v>
+      </c>
+      <c r="O9" s="10"/>
+      <c r="P9" s="9">
+        <f>N9*100+O9*25</f>
+        <v>2300</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A10" s="8">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A10" s="13">
         <v>8</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
       <c r="D10" s="2">
-        <v>3</v>
-      </c>
-      <c r="E10" s="2">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="E10" s="2"/>
       <c r="F10" s="2">
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2">
-        <v>2</v>
-      </c>
-      <c r="I10" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="I10" s="2">
+        <v>2</v>
+      </c>
       <c r="J10" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2">
         <v>2</v>
       </c>
       <c r="L10" s="2"/>
-      <c r="M10" s="12">
-        <f>SUM(C10:L10)</f>
-        <v>11</v>
-      </c>
+      <c r="M10" s="2"/>
       <c r="N10" s="11">
-        <v>1</v>
+        <f>SUM(C10:M10)</f>
+        <v>21</v>
       </c>
       <c r="O10" s="10">
-        <f>M10*100+N10*25</f>
-        <v>1125</v>
+        <v>4</v>
+      </c>
+      <c r="P10" s="9">
+        <f>N10*100+O10*25</f>
+        <v>2200</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A11" s="8">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A11" s="13">
         <v>9</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C11" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2">
         <v>3</v>
       </c>
-      <c r="E11" s="2"/>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
       <c r="I11" s="2">
         <v>1</v>
       </c>
       <c r="J11" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
       </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="12">
-        <f>SUM(C11:L11)</f>
-        <v>11</v>
-      </c>
+      <c r="L11" s="2">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2"/>
       <c r="N11" s="11">
-        <v>1</v>
+        <f>SUM(C11:M11)</f>
+        <v>17</v>
       </c>
       <c r="O11" s="10">
-        <f>M11*100+N11*25</f>
-        <v>1125</v>
+        <v>5</v>
+      </c>
+      <c r="P11" s="9">
+        <f>N11*100+O11*25</f>
+        <v>1825</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="8">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" s="13">
         <v>10</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="G12" s="2">
+        <v>2</v>
+      </c>
       <c r="H12" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" s="2">
         <v>3</v>
       </c>
-      <c r="K12" s="2"/>
+      <c r="K12" s="2">
+        <v>1</v>
+      </c>
       <c r="L12" s="2">
         <v>1</v>
       </c>
-      <c r="M12" s="12">
-        <f>SUM(C12:L12)</f>
-        <v>9</v>
-      </c>
-      <c r="N12" s="11"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="11">
+        <f>SUM(C12:M12)</f>
+        <v>17</v>
+      </c>
       <c r="O12" s="10">
-        <f>M12*100+N12*25</f>
-        <v>900</v>
+        <v>1</v>
+      </c>
+      <c r="P12" s="9">
+        <f>N12*100+O12*25</f>
+        <v>1725</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A13" s="8">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" s="13">
         <v>11</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
       <c r="D13" s="2">
         <v>1</v>
       </c>
@@ -1146,24 +1212,27 @@
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
-      <c r="M13" s="12">
-        <f>SUM(C13:L13)</f>
+      <c r="M13" s="2"/>
+      <c r="N13" s="11">
+        <f>SUM(C13:M13)</f>
         <v>4</v>
       </c>
-      <c r="N13" s="11"/>
-      <c r="O13" s="10">
-        <f>M13*100+N13*25</f>
+      <c r="O13" s="10"/>
+      <c r="P13" s="9">
+        <f>N13*100+O13*25</f>
         <v>400</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A14" s="8">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" s="13">
         <v>12</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -1177,19 +1246,20 @@
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
-      <c r="M14" s="12">
-        <f>SUM(C14:L14)</f>
-        <v>3</v>
-      </c>
-      <c r="N14" s="11"/>
-      <c r="O14" s="10">
-        <f>M14*100+N14*25</f>
+      <c r="M14" s="2"/>
+      <c r="N14" s="11">
+        <f>SUM(C14:M14)</f>
+        <v>3</v>
+      </c>
+      <c r="O14" s="10"/>
+      <c r="P14" s="9">
+        <f>N14*100+O14*25</f>
         <v>300</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O14">
-    <sortCondition descending="1" ref="O3:O14"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P14">
+    <sortCondition descending="1" ref="P3:P14"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
